--- a/advantest/dist/20261025_Advantest模型_v0.3.xlsx
+++ b/advantest/dist/20261025_Advantest模型_v0.3.xlsx
@@ -4048,7 +4048,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4341,7 +4341,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4638,7 +4638,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4789,7 +4789,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4960,7 +4960,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5111,7 +5111,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5273,7 +5273,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5500,7 +5500,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5712,7 +5712,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5863,7 +5863,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6120,7 +6120,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6271,7 +6271,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6433,7 +6433,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6584,7 +6584,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6824,7 +6824,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7192,7 +7192,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7316,7 +7316,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7515,7 +7515,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7636,7 +7636,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7757,7 +7757,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7878,7 +7878,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7999,7 +7999,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12074,7 +12074,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12664,7 +12664,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13119,7 +13119,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
